--- a/Encuestas de Satisfacción/Supervisor ev. por el Facilitador/Facilitador al Supervisor.xlsx
+++ b/Encuestas de Satisfacción/Supervisor ev. por el Facilitador/Facilitador al Supervisor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Benjo\Prácticas Laborales I\Reportes Automáticos\encuestas_app\Encuestas de Satisfacción\Supervisor ev. por el Facilitador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCAB7B5-4376-4661-9833-93424E8E2564}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41AE8B31-647C-406E-809F-BF624F8CCB56}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5232" yWindow="312" windowWidth="11472" windowHeight="12048" xr2:uid="{3BAEC8E7-747C-43CC-851E-1EE38F88BF4E}"/>
+    <workbookView xWindow="1080" yWindow="312" windowWidth="11472" windowHeight="12048" xr2:uid="{3BAEC8E7-747C-43CC-851E-1EE38F88BF4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -84,9 +84,6 @@
     <t>3.- ¿ El supervisor verificó que los recursos  materiales de aprendizaje estuvieran correctamente organizados y disponibles en la plataforma virtual antes del desarrollo de las actividades?.</t>
   </si>
   <si>
-    <t>4.- ¿El supervisor promovió una comunicación clara y oportuna con docente, facilitadores durante el desarrollo de la asignatura?.</t>
-  </si>
-  <si>
     <t>5.- ¿El supervisor realiza un seguimiento activo al desarrollo de las sesiones sincrónicas y brinda lineamientos sobre su pertinencia y calidad?.</t>
   </si>
   <si>
@@ -99,9 +96,6 @@
     <t>8.- ¿El supervisor coordina y verifica que las actividades de evaluación sean pertinentes y respondan al enfoque y los objetivos de aprendizaje de la asignatura?.</t>
   </si>
   <si>
-    <t>9.- ¿El supervisor coordina con los facilitadores la implementación de evaluaciones de satisfacción sobre el desarrollo de la asignatura (docente, contenido y metodología)?-</t>
-  </si>
-  <si>
     <t>10.- ¿Fomenta la reflexión entre los docentes y facilitadores sobre el proceso educativo para mejorar la experiencia de aprendizaje de los estudiantes?.</t>
   </si>
   <si>
@@ -121,6 +115,12 @@
   </si>
   <si>
     <t xml:space="preserve">RESPUESTAS ENVIADAS: </t>
+  </si>
+  <si>
+    <t>4.- ¿El supervisor promovió una comunicación clara y oportuna con docentes, facilitadores durante el desarrollo de la asignatura?.</t>
+  </si>
+  <si>
+    <t>9.- ¿El supervisor coordina con los facilitadores la implementación de evaluaciones de satisfacción sobre el desarrollo de la asignatura (docente, contenido y metodología)?</t>
   </si>
 </sst>
 </file>
@@ -501,10 +501,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD889BEF-E7CF-404E-B88D-A9D57711BFD4}">
   <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="158.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -544,7 +547,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -554,7 +557,7 @@
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -670,7 +673,7 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C18" s="4">
         <v>3</v>
@@ -694,7 +697,7 @@
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="4">
         <v>3</v>
@@ -718,7 +721,7 @@
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="4">
         <v>3</v>
@@ -742,7 +745,7 @@
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="4">
         <v>3</v>
@@ -766,7 +769,7 @@
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="4">
         <v>3</v>
@@ -790,7 +793,7 @@
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C23" s="4">
         <v>3</v>
@@ -814,7 +817,7 @@
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C24" s="4">
         <v>3</v>
@@ -838,7 +841,7 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C25" s="4">
         <v>3</v>
@@ -861,10 +864,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="4"/>
@@ -876,7 +879,7 @@
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="4"/>
@@ -888,7 +891,7 @@
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="4"/>
